--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,6 +1716,516 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127304107</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>473906</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6727046</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127304344</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>473870</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6726909</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127304018</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96562</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>473699</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6726833</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127304282</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>473559</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6727112</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127304301</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>473659</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6727043</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,7 +1721,7 @@
         <v>127304107</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96562</v>
+        <v>96568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>127304282</v>
       </c>
       <c r="B13" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>127304301</v>
       </c>
       <c r="B14" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2226,6 +2226,2815 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127331366</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>473439</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6727269</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127331172</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>473640</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6727005</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127331094</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92615</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>473644</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6726994</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127330938</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>473748</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6726825</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127331002</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>473724</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6726784</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127330814</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>473929</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6726988</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127331196</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>473627</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6726997</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127331018</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>473726</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6726792</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127331745</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>473791</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6727140</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127330976</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>473742</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6726796</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127330753</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>473944</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6727005</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127331403</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>473560</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6727318</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127331386</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>473513</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6727259</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127331634</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>473601</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6727359</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127331698</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>473823</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6727122</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127331707</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>473813</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6727113</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127331596</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>473535</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6727379</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127331731</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>473794</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6727108</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127331652</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>473946</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6726976</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127331133</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>473662</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6727012</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127331217</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>473606</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6727012</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127331657</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>473601</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6727336</v>
+      </c>
+      <c r="S36" t="n">
+        <v>50</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127331066</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92615</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>473697</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6726976</v>
+      </c>
+      <c r="S37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127330902</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>473772</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6726854</v>
+      </c>
+      <c r="S38" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127330843</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>473864</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6726930</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127331719</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>473802</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6727121</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2764,46 +2764,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127330814</v>
+        <v>127331196</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>56849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2811,10 +2807,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473929</v>
+        <v>473627</v>
       </c>
       <c r="R20" t="n">
-        <v>6726988</v>
+        <v>6726997</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2855,7 +2851,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2874,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B21" t="n">
-        <v>56849</v>
+        <v>98476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,31 +2880,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2917,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R21" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2961,6 +2960,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2979,42 +2979,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331018</v>
+        <v>127330814</v>
       </c>
       <c r="B22" t="n">
-        <v>98476</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473726</v>
+        <v>473929</v>
       </c>
       <c r="R22" t="n">
-        <v>6726792</v>
+        <v>6726988</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3089,7 +3089,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127331745</v>
+        <v>127330976</v>
       </c>
       <c r="B23" t="n">
         <v>98442</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473791</v>
+        <v>473742</v>
       </c>
       <c r="R23" t="n">
-        <v>6727140</v>
+        <v>6726796</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127330976</v>
+        <v>127331745</v>
       </c>
       <c r="B24" t="n">
         <v>98442</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473742</v>
+        <v>473791</v>
       </c>
       <c r="R24" t="n">
-        <v>6726796</v>
+        <v>6727140</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331403</v>
+        <v>127331386</v>
       </c>
       <c r="B26" t="n">
         <v>57657</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473560</v>
+        <v>473513</v>
       </c>
       <c r="R26" t="n">
-        <v>6727318</v>
+        <v>6727259</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,7 +3529,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331386</v>
+        <v>127331403</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473513</v>
+        <v>473560</v>
       </c>
       <c r="R27" t="n">
-        <v>6727259</v>
+        <v>6727318</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4184,10 +4184,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331652</v>
+        <v>127331133</v>
       </c>
       <c r="B33" t="n">
-        <v>91345</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4195,30 +4195,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4226,10 +4227,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473946</v>
+        <v>473662</v>
       </c>
       <c r="R33" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4264,13 +4265,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4289,32 +4294,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331133</v>
+        <v>127331217</v>
       </c>
       <c r="B34" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4322,7 +4327,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4332,7 +4337,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473662</v>
+        <v>473606</v>
       </c>
       <c r="R34" t="n">
         <v>6727012</v>
@@ -4368,11 +4373,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,42 +4399,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331217</v>
+        <v>127331652</v>
       </c>
       <c r="B35" t="n">
-        <v>56849</v>
+        <v>91345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4442,10 +4441,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473606</v>
+        <v>473946</v>
       </c>
       <c r="R35" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4486,6 +4485,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330902</v>
+        <v>127330843</v>
       </c>
       <c r="B38" t="n">
         <v>98442</v>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473772</v>
+        <v>473864</v>
       </c>
       <c r="R38" t="n">
-        <v>6726854</v>
+        <v>6726930</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4821,7 +4821,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127330843</v>
+        <v>127331719</v>
       </c>
       <c r="B39" t="n">
         <v>98442</v>
@@ -4851,14 +4851,10 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4868,10 +4864,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473864</v>
+        <v>473802</v>
       </c>
       <c r="R39" t="n">
-        <v>6726930</v>
+        <v>6727121</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4931,7 +4927,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331719</v>
+        <v>127330902</v>
       </c>
       <c r="B40" t="n">
         <v>98442</v>
@@ -4961,10 +4957,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473802</v>
+        <v>473772</v>
       </c>
       <c r="R40" t="n">
-        <v>6727121</v>
+        <v>6726854</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5035,6 +5035,113 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127360815</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Djupsjön, Djupsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>473865</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6726960</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Foto finns</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96568</v>
+        <v>96569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>127331094</v>
       </c>
       <c r="B17" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>127330938</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>127331002</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>127331018</v>
       </c>
       <c r="B21" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>127330814</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3089,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127330976</v>
+        <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473742</v>
+        <v>473944</v>
       </c>
       <c r="R23" t="n">
-        <v>6726796</v>
+        <v>6727005</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127330753</v>
+        <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473944</v>
+        <v>473742</v>
       </c>
       <c r="R25" t="n">
-        <v>6727005</v>
+        <v>6726796</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331386</v>
+        <v>127331403</v>
       </c>
       <c r="B26" t="n">
         <v>57657</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473513</v>
+        <v>473560</v>
       </c>
       <c r="R26" t="n">
-        <v>6727259</v>
+        <v>6727318</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,7 +3529,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331403</v>
+        <v>127331386</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473560</v>
+        <v>473513</v>
       </c>
       <c r="R27" t="n">
-        <v>6727318</v>
+        <v>6727259</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3862,7 +3862,7 @@
         <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>127331596</v>
       </c>
       <c r="B31" t="n">
-        <v>92609</v>
+        <v>92610</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4294,42 +4294,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331217</v>
+        <v>127331652</v>
       </c>
       <c r="B34" t="n">
-        <v>56849</v>
+        <v>91346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4337,10 +4336,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473606</v>
+        <v>473946</v>
       </c>
       <c r="R34" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4381,6 +4380,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4399,41 +4399,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331652</v>
+        <v>127331217</v>
       </c>
       <c r="B35" t="n">
-        <v>91345</v>
+        <v>56849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4441,10 +4442,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473946</v>
+        <v>473606</v>
       </c>
       <c r="R35" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4485,7 +4486,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>127331066</v>
       </c>
       <c r="B37" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330843</v>
+        <v>127330902</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473864</v>
+        <v>473772</v>
       </c>
       <c r="R38" t="n">
-        <v>6726930</v>
+        <v>6726854</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4821,10 +4821,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127331719</v>
+        <v>127330843</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4851,10 +4851,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4864,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473802</v>
+        <v>473864</v>
       </c>
       <c r="R39" t="n">
-        <v>6727121</v>
+        <v>6726930</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4927,10 +4931,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127330902</v>
+        <v>127331719</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4957,14 +4961,10 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473772</v>
+        <v>473802</v>
       </c>
       <c r="R40" t="n">
-        <v>6726854</v>
+        <v>6727121</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2869,42 +2869,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331018</v>
+        <v>127330814</v>
       </c>
       <c r="B21" t="n">
-        <v>98477</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473726</v>
+        <v>473929</v>
       </c>
       <c r="R21" t="n">
-        <v>6726792</v>
+        <v>6726988</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2979,42 +2979,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127330814</v>
+        <v>127331018</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98477</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473929</v>
+        <v>473726</v>
       </c>
       <c r="R22" t="n">
-        <v>6726988</v>
+        <v>6726792</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2439,41 +2439,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331094</v>
+        <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2481,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473644</v>
+        <v>473748</v>
       </c>
       <c r="R17" t="n">
-        <v>6726994</v>
+        <v>6726825</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2544,7 +2549,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127330938</v>
+        <v>127331002</v>
       </c>
       <c r="B18" t="n">
         <v>98443</v>
@@ -2574,7 +2579,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473748</v>
+        <v>473724</v>
       </c>
       <c r="R18" t="n">
-        <v>6726825</v>
+        <v>6726784</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2654,46 +2659,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331002</v>
+        <v>127331094</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473724</v>
+        <v>473644</v>
       </c>
       <c r="R19" t="n">
-        <v>6726784</v>
+        <v>6726994</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B20" t="n">
-        <v>56849</v>
+        <v>98477</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,31 +2775,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2807,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R20" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2851,6 +2855,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2979,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331018</v>
+        <v>127331196</v>
       </c>
       <c r="B22" t="n">
-        <v>98477</v>
+        <v>56849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,35 +2995,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3026,10 +3027,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473726</v>
+        <v>473627</v>
       </c>
       <c r="R22" t="n">
-        <v>6726792</v>
+        <v>6726997</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3070,7 +3071,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3749,42 +3749,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331698</v>
+        <v>127331707</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3792,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473823</v>
+        <v>473813</v>
       </c>
       <c r="R29" t="n">
-        <v>6727122</v>
+        <v>6727113</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3830,17 +3834,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,46 +3859,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331707</v>
+        <v>127331698</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3906,10 +3902,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473813</v>
+        <v>473823</v>
       </c>
       <c r="R30" t="n">
-        <v>6727113</v>
+        <v>6727122</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3944,13 +3940,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4184,32 +4184,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331133</v>
+        <v>127331217</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473662</v>
+        <v>473606</v>
       </c>
       <c r="R33" t="n">
         <v>6727012</v>
@@ -4263,11 +4263,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4399,32 +4394,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331217</v>
+        <v>127331133</v>
       </c>
       <c r="B35" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4432,7 +4427,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4442,7 +4437,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473606</v>
+        <v>473662</v>
       </c>
       <c r="R35" t="n">
         <v>6727012</v>
@@ -4478,6 +4473,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4605,37 +4605,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127331066</v>
+        <v>127330902</v>
       </c>
       <c r="B37" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4643,10 +4652,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473697</v>
+        <v>473772</v>
       </c>
       <c r="R37" t="n">
-        <v>6726976</v>
+        <v>6726854</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4679,11 +4688,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4711,7 +4715,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330902</v>
+        <v>127330843</v>
       </c>
       <c r="B38" t="n">
         <v>98443</v>
@@ -4741,7 +4745,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4758,10 +4762,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473772</v>
+        <v>473864</v>
       </c>
       <c r="R38" t="n">
-        <v>6726854</v>
+        <v>6726930</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4821,7 +4825,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127330843</v>
+        <v>127331719</v>
       </c>
       <c r="B39" t="n">
         <v>98443</v>
@@ -4851,14 +4855,10 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473864</v>
+        <v>473802</v>
       </c>
       <c r="R39" t="n">
-        <v>6726930</v>
+        <v>6727121</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4931,42 +4931,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331719</v>
+        <v>127331066</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4974,10 +4969,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473802</v>
+        <v>473697</v>
       </c>
       <c r="R40" t="n">
-        <v>6727121</v>
+        <v>6726976</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5010,6 +5005,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2439,46 +2439,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127330938</v>
+        <v>127331094</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2486,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473748</v>
+        <v>473644</v>
       </c>
       <c r="R17" t="n">
-        <v>6726825</v>
+        <v>6726994</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2549,7 +2544,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331002</v>
+        <v>127330938</v>
       </c>
       <c r="B18" t="n">
         <v>98443</v>
@@ -2579,7 +2574,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473724</v>
+        <v>473748</v>
       </c>
       <c r="R18" t="n">
-        <v>6726784</v>
+        <v>6726825</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2659,41 +2654,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331094</v>
+        <v>127331002</v>
       </c>
       <c r="B19" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473644</v>
+        <v>473724</v>
       </c>
       <c r="R19" t="n">
-        <v>6726994</v>
+        <v>6726784</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -4605,46 +4605,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127330902</v>
+        <v>127331066</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4652,10 +4643,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473772</v>
+        <v>473697</v>
       </c>
       <c r="R37" t="n">
-        <v>6726854</v>
+        <v>6726976</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4688,6 +4679,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4715,7 +4711,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330843</v>
+        <v>127330902</v>
       </c>
       <c r="B38" t="n">
         <v>98443</v>
@@ -4745,7 +4741,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4762,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473864</v>
+        <v>473772</v>
       </c>
       <c r="R38" t="n">
-        <v>6726930</v>
+        <v>6726854</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4825,7 +4821,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127331719</v>
+        <v>127330843</v>
       </c>
       <c r="B39" t="n">
         <v>98443</v>
@@ -4855,10 +4851,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473802</v>
+        <v>473864</v>
       </c>
       <c r="R39" t="n">
-        <v>6727121</v>
+        <v>6726930</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4931,37 +4931,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331066</v>
+        <v>127331719</v>
       </c>
       <c r="B40" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473697</v>
+        <v>473802</v>
       </c>
       <c r="R40" t="n">
-        <v>6726976</v>
+        <v>6727121</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5005,11 +5010,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2439,41 +2439,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331094</v>
+        <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2481,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473644</v>
+        <v>473748</v>
       </c>
       <c r="R17" t="n">
-        <v>6726994</v>
+        <v>6726825</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2544,7 +2549,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127330938</v>
+        <v>127331002</v>
       </c>
       <c r="B18" t="n">
         <v>98443</v>
@@ -2574,7 +2579,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473748</v>
+        <v>473724</v>
       </c>
       <c r="R18" t="n">
-        <v>6726825</v>
+        <v>6726784</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2654,46 +2659,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331002</v>
+        <v>127331094</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473724</v>
+        <v>473644</v>
       </c>
       <c r="R19" t="n">
-        <v>6726784</v>
+        <v>6726994</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>127304107</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>127304344</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96569</v>
+        <v>96573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>127304282</v>
       </c>
       <c r="B13" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>127304301</v>
       </c>
       <c r="B14" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>127331366</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127331172</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>127331002</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127331094</v>
       </c>
       <c r="B19" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331018</v>
+        <v>127331196</v>
       </c>
       <c r="B20" t="n">
-        <v>98477</v>
+        <v>56853</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,35 +2775,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2811,10 +2807,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473726</v>
+        <v>473627</v>
       </c>
       <c r="R20" t="n">
-        <v>6726792</v>
+        <v>6726997</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2855,7 +2851,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2877,7 +2872,7 @@
         <v>127330814</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B22" t="n">
-        <v>56849</v>
+        <v>98481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,31 +2990,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3027,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R22" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3071,6 +3070,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331403</v>
+        <v>127331386</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473560</v>
+        <v>473513</v>
       </c>
       <c r="R26" t="n">
-        <v>6727318</v>
+        <v>6727259</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331386</v>
+        <v>127331403</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473513</v>
+        <v>473560</v>
       </c>
       <c r="R27" t="n">
-        <v>6727259</v>
+        <v>6727318</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3642,7 +3642,7 @@
         <v>127331634</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3749,46 +3749,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331707</v>
+        <v>127331698</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3796,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473813</v>
+        <v>473823</v>
       </c>
       <c r="R29" t="n">
-        <v>6727113</v>
+        <v>6727122</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3834,13 +3830,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,42 +3859,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331698</v>
+        <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3902,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473823</v>
+        <v>473813</v>
       </c>
       <c r="R30" t="n">
-        <v>6727122</v>
+        <v>6727113</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3940,17 +3944,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>127331596</v>
       </c>
       <c r="B31" t="n">
-        <v>92610</v>
+        <v>92614</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4184,42 +4184,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331217</v>
+        <v>127331652</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4227,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473606</v>
+        <v>473946</v>
       </c>
       <c r="R33" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4271,6 +4270,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4289,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331652</v>
+        <v>127331133</v>
       </c>
       <c r="B34" t="n">
-        <v>91346</v>
+        <v>57661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,30 +4300,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4331,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473946</v>
+        <v>473662</v>
       </c>
       <c r="R34" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4369,13 +4370,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4394,32 +4399,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331133</v>
+        <v>127331217</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>56853</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4427,7 +4432,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4437,7 +4442,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473662</v>
+        <v>473606</v>
       </c>
       <c r="R35" t="n">
         <v>6727012</v>
@@ -4473,11 +4478,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4507,7 +4507,7 @@
         <v>127331657</v>
       </c>
       <c r="B36" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>127331066</v>
       </c>
       <c r="B37" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>127330902</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>127330843</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>127331719</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>127360815</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2439,46 +2439,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127330938</v>
+        <v>127331094</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2486,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473748</v>
+        <v>473644</v>
       </c>
       <c r="R17" t="n">
-        <v>6726825</v>
+        <v>6726994</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2549,7 +2544,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331002</v>
+        <v>127330938</v>
       </c>
       <c r="B18" t="n">
         <v>98447</v>
@@ -2579,7 +2574,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473724</v>
+        <v>473748</v>
       </c>
       <c r="R18" t="n">
-        <v>6726784</v>
+        <v>6726825</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2659,41 +2654,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331094</v>
+        <v>127331002</v>
       </c>
       <c r="B19" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473644</v>
+        <v>473724</v>
       </c>
       <c r="R19" t="n">
-        <v>6726994</v>
+        <v>6726784</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2869,42 +2869,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127330814</v>
+        <v>127331018</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473929</v>
+        <v>473726</v>
       </c>
       <c r="R21" t="n">
-        <v>6726988</v>
+        <v>6726792</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2979,42 +2979,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331018</v>
+        <v>127330814</v>
       </c>
       <c r="B22" t="n">
-        <v>98481</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473726</v>
+        <v>473929</v>
       </c>
       <c r="R22" t="n">
-        <v>6726792</v>
+        <v>6726988</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331386</v>
+        <v>127331403</v>
       </c>
       <c r="B26" t="n">
         <v>57661</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473513</v>
+        <v>473560</v>
       </c>
       <c r="R26" t="n">
-        <v>6727259</v>
+        <v>6727318</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,7 +3529,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331403</v>
+        <v>127331386</v>
       </c>
       <c r="B27" t="n">
         <v>57661</v>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473560</v>
+        <v>473513</v>
       </c>
       <c r="R27" t="n">
-        <v>6727318</v>
+        <v>6727259</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3749,42 +3749,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331698</v>
+        <v>127331707</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3792,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473823</v>
+        <v>473813</v>
       </c>
       <c r="R29" t="n">
-        <v>6727122</v>
+        <v>6727113</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3830,17 +3834,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,46 +3859,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331707</v>
+        <v>127331698</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3906,10 +3902,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473813</v>
+        <v>473823</v>
       </c>
       <c r="R30" t="n">
-        <v>6727113</v>
+        <v>6727122</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3944,13 +3940,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331652</v>
+        <v>127331133</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4195,30 +4195,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4226,10 +4227,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473946</v>
+        <v>473662</v>
       </c>
       <c r="R33" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4264,13 +4265,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4289,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331133</v>
+        <v>127331652</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,31 +4305,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4332,10 +4336,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473662</v>
+        <v>473946</v>
       </c>
       <c r="R34" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4370,17 +4374,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2439,41 +2439,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331094</v>
+        <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2481,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473644</v>
+        <v>473748</v>
       </c>
       <c r="R17" t="n">
-        <v>6726994</v>
+        <v>6726825</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2544,7 +2549,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127330938</v>
+        <v>127331002</v>
       </c>
       <c r="B18" t="n">
         <v>98447</v>
@@ -2574,7 +2579,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473748</v>
+        <v>473724</v>
       </c>
       <c r="R18" t="n">
-        <v>6726825</v>
+        <v>6726784</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2654,46 +2659,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331002</v>
+        <v>127331094</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473724</v>
+        <v>473644</v>
       </c>
       <c r="R19" t="n">
-        <v>6726784</v>
+        <v>6726994</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B20" t="n">
-        <v>56853</v>
+        <v>98481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,31 +2775,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2807,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R20" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2851,6 +2855,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2869,42 +2874,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331018</v>
+        <v>127330814</v>
       </c>
       <c r="B21" t="n">
-        <v>98481</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2916,10 +2921,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473726</v>
+        <v>473929</v>
       </c>
       <c r="R21" t="n">
-        <v>6726792</v>
+        <v>6726988</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2979,46 +2984,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127330814</v>
+        <v>127331196</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3026,10 +3027,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473929</v>
+        <v>473627</v>
       </c>
       <c r="R22" t="n">
-        <v>6726988</v>
+        <v>6726997</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3070,7 +3071,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4184,32 +4184,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331133</v>
+        <v>127331217</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473662</v>
+        <v>473606</v>
       </c>
       <c r="R33" t="n">
         <v>6727012</v>
@@ -4263,11 +4263,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331652</v>
+        <v>127331133</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>57661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4305,30 +4300,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4336,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473946</v>
+        <v>473662</v>
       </c>
       <c r="R34" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4374,13 +4370,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4399,42 +4399,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331217</v>
+        <v>127331652</v>
       </c>
       <c r="B35" t="n">
-        <v>56853</v>
+        <v>91350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4442,10 +4441,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473606</v>
+        <v>473946</v>
       </c>
       <c r="R35" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4486,6 +4485,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -3749,46 +3749,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331707</v>
+        <v>127331698</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3796,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473813</v>
+        <v>473823</v>
       </c>
       <c r="R29" t="n">
-        <v>6727113</v>
+        <v>6727122</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3834,13 +3830,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,42 +3859,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331698</v>
+        <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3902,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473823</v>
+        <v>473813</v>
       </c>
       <c r="R30" t="n">
-        <v>6727122</v>
+        <v>6727113</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3940,17 +3944,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2442,7 +2442,7 @@
         <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>127331002</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331018</v>
+        <v>127331196</v>
       </c>
       <c r="B20" t="n">
-        <v>98481</v>
+        <v>56853</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,35 +2775,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2811,10 +2807,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473726</v>
+        <v>473627</v>
       </c>
       <c r="R20" t="n">
-        <v>6726792</v>
+        <v>6726997</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2855,7 +2851,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2877,7 +2872,7 @@
         <v>127330814</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B22" t="n">
-        <v>56853</v>
+        <v>98482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,31 +2990,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3027,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R22" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3071,6 +3070,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4184,42 +4184,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331217</v>
+        <v>127331652</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4227,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473606</v>
+        <v>473946</v>
       </c>
       <c r="R33" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4271,6 +4270,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4399,41 +4399,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331652</v>
+        <v>127331217</v>
       </c>
       <c r="B35" t="n">
-        <v>91350</v>
+        <v>56853</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4441,10 +4442,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473946</v>
+        <v>473606</v>
       </c>
       <c r="R35" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4485,7 +4486,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>127330902</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>127330843</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>127331719</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2439,46 +2439,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127330938</v>
+        <v>127331094</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>92620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2486,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473748</v>
+        <v>473644</v>
       </c>
       <c r="R17" t="n">
-        <v>6726825</v>
+        <v>6726994</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2549,7 +2544,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331002</v>
+        <v>127330938</v>
       </c>
       <c r="B18" t="n">
         <v>98448</v>
@@ -2579,7 +2574,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473724</v>
+        <v>473748</v>
       </c>
       <c r="R18" t="n">
-        <v>6726784</v>
+        <v>6726825</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2659,41 +2654,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331094</v>
+        <v>127331002</v>
       </c>
       <c r="B19" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473644</v>
+        <v>473724</v>
       </c>
       <c r="R19" t="n">
-        <v>6726994</v>
+        <v>6726784</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>127304107</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>127304344</v>
       </c>
       <c r="B11" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96573</v>
+        <v>96575</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>127304282</v>
       </c>
       <c r="B13" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>127304301</v>
       </c>
       <c r="B14" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>127331366</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127331172</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>127331094</v>
       </c>
       <c r="B17" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>127330938</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>127331002</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B20" t="n">
-        <v>56853</v>
+        <v>98484</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,31 +2775,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2807,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R20" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2851,6 +2855,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2869,46 +2874,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127330814</v>
+        <v>127331196</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>56855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2916,10 +2917,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473929</v>
+        <v>473627</v>
       </c>
       <c r="R21" t="n">
-        <v>6726988</v>
+        <v>6726997</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2960,7 +2961,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2979,42 +2979,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331018</v>
+        <v>127330814</v>
       </c>
       <c r="B22" t="n">
-        <v>98482</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473726</v>
+        <v>473929</v>
       </c>
       <c r="R22" t="n">
-        <v>6726792</v>
+        <v>6726988</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3092,7 +3092,7 @@
         <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>127331403</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>127331386</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>127331634</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>127331698</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>127331596</v>
       </c>
       <c r="B31" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>127331652</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4289,32 +4289,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331133</v>
+        <v>127331217</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>56855</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4322,7 +4322,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473662</v>
+        <v>473606</v>
       </c>
       <c r="R34" t="n">
         <v>6727012</v>
@@ -4368,11 +4368,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,32 +4394,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331217</v>
+        <v>127331133</v>
       </c>
       <c r="B35" t="n">
-        <v>56853</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4432,7 +4427,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4442,7 +4437,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473606</v>
+        <v>473662</v>
       </c>
       <c r="R35" t="n">
         <v>6727012</v>
@@ -4478,6 +4473,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4507,7 +4507,7 @@
         <v>127331657</v>
       </c>
       <c r="B36" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,37 +4605,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127331066</v>
+        <v>127331719</v>
       </c>
       <c r="B37" t="n">
-        <v>92620</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4643,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473697</v>
+        <v>473802</v>
       </c>
       <c r="R37" t="n">
-        <v>6726976</v>
+        <v>6727121</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4679,11 +4684,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,7 +4714,7 @@
         <v>127330902</v>
       </c>
       <c r="B38" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>127330843</v>
       </c>
       <c r="B39" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4931,42 +4931,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331719</v>
+        <v>127331066</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>92622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4974,10 +4969,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473802</v>
+        <v>473697</v>
       </c>
       <c r="R40" t="n">
-        <v>6727121</v>
+        <v>6726976</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5010,6 +5005,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5040,7 +5040,7 @@
         <v>127360815</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -4289,32 +4289,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331217</v>
+        <v>127331133</v>
       </c>
       <c r="B34" t="n">
-        <v>56855</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4322,7 +4322,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473606</v>
+        <v>473662</v>
       </c>
       <c r="R34" t="n">
         <v>6727012</v>
@@ -4368,6 +4368,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4394,32 +4399,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331133</v>
+        <v>127331217</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4427,7 +4432,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4437,7 +4442,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473662</v>
+        <v>473606</v>
       </c>
       <c r="R35" t="n">
         <v>6727012</v>
@@ -4473,11 +4478,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4605,42 +4605,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127331719</v>
+        <v>127331066</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4648,10 +4643,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473802</v>
+        <v>473697</v>
       </c>
       <c r="R37" t="n">
-        <v>6727121</v>
+        <v>6726976</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4684,6 +4679,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4931,37 +4931,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331066</v>
+        <v>127331719</v>
       </c>
       <c r="B40" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473697</v>
+        <v>473802</v>
       </c>
       <c r="R40" t="n">
-        <v>6726976</v>
+        <v>6727121</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5005,11 +5010,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331018</v>
+        <v>127331196</v>
       </c>
       <c r="B20" t="n">
-        <v>98484</v>
+        <v>56855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,35 +2775,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2811,10 +2807,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473726</v>
+        <v>473627</v>
       </c>
       <c r="R20" t="n">
-        <v>6726792</v>
+        <v>6726997</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2855,7 +2851,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2874,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B21" t="n">
-        <v>56855</v>
+        <v>98484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,31 +2880,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2917,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R21" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2961,6 +2960,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96575</v>
+        <v>96581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2439,41 +2439,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331094</v>
+        <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>92622</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2481,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473644</v>
+        <v>473748</v>
       </c>
       <c r="R17" t="n">
-        <v>6726994</v>
+        <v>6726825</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2544,10 +2549,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127330938</v>
+        <v>127331002</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2579,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473748</v>
+        <v>473724</v>
       </c>
       <c r="R18" t="n">
-        <v>6726825</v>
+        <v>6726784</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2654,46 +2659,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331002</v>
+        <v>127331094</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>92628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473724</v>
+        <v>473644</v>
       </c>
       <c r="R19" t="n">
-        <v>6726784</v>
+        <v>6726994</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2872,7 +2872,7 @@
         <v>127331018</v>
       </c>
       <c r="B21" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>127330814</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>127331596</v>
       </c>
       <c r="B31" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4184,41 +4184,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331652</v>
+        <v>127331217</v>
       </c>
       <c r="B33" t="n">
-        <v>91352</v>
+        <v>56855</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4226,10 +4227,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473946</v>
+        <v>473606</v>
       </c>
       <c r="R33" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4270,7 +4271,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4399,42 +4399,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331217</v>
+        <v>127331652</v>
       </c>
       <c r="B35" t="n">
-        <v>56855</v>
+        <v>91358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4442,10 +4441,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473606</v>
+        <v>473946</v>
       </c>
       <c r="R35" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4486,6 +4485,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>127331066</v>
       </c>
       <c r="B37" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>127330902</v>
       </c>
       <c r="B38" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>127330843</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>127331719</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>127304107</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>127304344</v>
       </c>
       <c r="B11" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96581</v>
+        <v>96584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>127304282</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>127304301</v>
       </c>
       <c r="B14" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>127331366</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127331172</v>
       </c>
       <c r="B16" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,46 +2439,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127330938</v>
+        <v>127331094</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>92631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2486,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473748</v>
+        <v>473644</v>
       </c>
       <c r="R17" t="n">
-        <v>6726825</v>
+        <v>6726994</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2549,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331002</v>
+        <v>127330938</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2574,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473724</v>
+        <v>473748</v>
       </c>
       <c r="R18" t="n">
-        <v>6726784</v>
+        <v>6726825</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2659,41 +2654,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331094</v>
+        <v>127331002</v>
       </c>
       <c r="B19" t="n">
-        <v>92628</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473644</v>
+        <v>473724</v>
       </c>
       <c r="R19" t="n">
-        <v>6726994</v>
+        <v>6726784</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2767,7 +2767,7 @@
         <v>127331196</v>
       </c>
       <c r="B20" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,42 +2869,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331018</v>
+        <v>127330814</v>
       </c>
       <c r="B21" t="n">
-        <v>98490</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473726</v>
+        <v>473929</v>
       </c>
       <c r="R21" t="n">
-        <v>6726792</v>
+        <v>6726988</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2979,42 +2979,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127330814</v>
+        <v>127331018</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473929</v>
+        <v>473726</v>
       </c>
       <c r="R22" t="n">
-        <v>6726988</v>
+        <v>6726792</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3092,7 +3092,7 @@
         <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>127331403</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>127331386</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>127331634</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>127331698</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>127331596</v>
       </c>
       <c r="B31" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>127331217</v>
       </c>
       <c r="B33" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4289,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331133</v>
+        <v>127331652</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>91361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,31 +4300,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4332,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473662</v>
+        <v>473946</v>
       </c>
       <c r="R34" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4370,17 +4369,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4399,10 +4394,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331652</v>
+        <v>127331133</v>
       </c>
       <c r="B35" t="n">
-        <v>91358</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4410,30 +4405,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4441,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473946</v>
+        <v>473662</v>
       </c>
       <c r="R35" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4479,13 +4475,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>127331657</v>
       </c>
       <c r="B36" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,37 +4605,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127331066</v>
+        <v>127330902</v>
       </c>
       <c r="B37" t="n">
-        <v>92628</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4643,10 +4652,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473697</v>
+        <v>473772</v>
       </c>
       <c r="R37" t="n">
-        <v>6726976</v>
+        <v>6726854</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4679,11 +4688,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4711,10 +4715,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330902</v>
+        <v>127330843</v>
       </c>
       <c r="B38" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4741,7 +4745,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4758,10 +4762,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473772</v>
+        <v>473864</v>
       </c>
       <c r="R38" t="n">
-        <v>6726854</v>
+        <v>6726930</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4821,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127330843</v>
+        <v>127331719</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4851,14 +4855,10 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473864</v>
+        <v>473802</v>
       </c>
       <c r="R39" t="n">
-        <v>6726930</v>
+        <v>6727121</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4931,42 +4931,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331719</v>
+        <v>127331066</v>
       </c>
       <c r="B40" t="n">
-        <v>98456</v>
+        <v>92631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4974,10 +4969,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473802</v>
+        <v>473697</v>
       </c>
       <c r="R40" t="n">
-        <v>6727121</v>
+        <v>6726976</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5010,6 +5005,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5040,7 +5040,7 @@
         <v>127360815</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>127304107</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>127304344</v>
       </c>
       <c r="B11" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96584</v>
+        <v>96592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>127304282</v>
       </c>
       <c r="B13" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>127304301</v>
       </c>
       <c r="B14" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>127331366</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127331172</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,41 +2439,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331094</v>
+        <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>92631</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2481,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473644</v>
+        <v>473748</v>
       </c>
       <c r="R17" t="n">
-        <v>6726994</v>
+        <v>6726825</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2544,10 +2549,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127330938</v>
+        <v>127331002</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2579,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473748</v>
+        <v>473724</v>
       </c>
       <c r="R18" t="n">
-        <v>6726825</v>
+        <v>6726784</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2654,46 +2659,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331002</v>
+        <v>127331094</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>92639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473724</v>
+        <v>473644</v>
       </c>
       <c r="R19" t="n">
-        <v>6726784</v>
+        <v>6726994</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2764,42 +2764,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331196</v>
+        <v>127330814</v>
       </c>
       <c r="B20" t="n">
-        <v>56858</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2807,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473627</v>
+        <v>473929</v>
       </c>
       <c r="R20" t="n">
-        <v>6726997</v>
+        <v>6726988</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2851,6 +2855,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2869,46 +2874,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127330814</v>
+        <v>127331196</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>56864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2916,10 +2917,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473929</v>
+        <v>473627</v>
       </c>
       <c r="R21" t="n">
-        <v>6726988</v>
+        <v>6726997</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2960,7 +2961,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>127331018</v>
       </c>
       <c r="B22" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>127331403</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>127331386</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>127331634</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3749,42 +3749,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331698</v>
+        <v>127331707</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3792,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473823</v>
+        <v>473813</v>
       </c>
       <c r="R29" t="n">
-        <v>6727122</v>
+        <v>6727113</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3830,17 +3834,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,46 +3859,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331707</v>
+        <v>127331698</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3906,10 +3902,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473813</v>
+        <v>473823</v>
       </c>
       <c r="R30" t="n">
-        <v>6727113</v>
+        <v>6727122</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3944,13 +3940,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>127331596</v>
       </c>
       <c r="B31" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4184,42 +4184,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331217</v>
+        <v>127331652</v>
       </c>
       <c r="B33" t="n">
-        <v>56858</v>
+        <v>91369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4227,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473606</v>
+        <v>473946</v>
       </c>
       <c r="R33" t="n">
-        <v>6727012</v>
+        <v>6726976</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4271,6 +4270,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4289,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331652</v>
+        <v>127331133</v>
       </c>
       <c r="B34" t="n">
-        <v>91361</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,30 +4300,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4331,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473946</v>
+        <v>473662</v>
       </c>
       <c r="R34" t="n">
-        <v>6726976</v>
+        <v>6727012</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4369,13 +4370,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4394,32 +4399,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331133</v>
+        <v>127331217</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>56864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4427,7 +4432,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4437,7 +4442,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473662</v>
+        <v>473606</v>
       </c>
       <c r="R35" t="n">
         <v>6727012</v>
@@ -4473,11 +4478,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4507,7 +4507,7 @@
         <v>127331657</v>
       </c>
       <c r="B36" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,46 +4605,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127330902</v>
+        <v>127331066</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>92639</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4652,10 +4643,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473772</v>
+        <v>473697</v>
       </c>
       <c r="R37" t="n">
-        <v>6726854</v>
+        <v>6726976</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4688,6 +4679,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4715,10 +4711,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330843</v>
+        <v>127330902</v>
       </c>
       <c r="B38" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4741,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4762,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473864</v>
+        <v>473772</v>
       </c>
       <c r="R38" t="n">
-        <v>6726930</v>
+        <v>6726854</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4825,10 +4821,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127331719</v>
+        <v>127330843</v>
       </c>
       <c r="B39" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,10 +4851,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473802</v>
+        <v>473864</v>
       </c>
       <c r="R39" t="n">
-        <v>6727121</v>
+        <v>6726930</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4931,37 +4931,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331066</v>
+        <v>127331719</v>
       </c>
       <c r="B40" t="n">
-        <v>92631</v>
+        <v>98467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473697</v>
+        <v>473802</v>
       </c>
       <c r="R40" t="n">
-        <v>6726976</v>
+        <v>6727121</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5005,11 +5010,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5040,7 +5040,7 @@
         <v>127360815</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96592</v>
+        <v>96593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2439,46 +2439,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127330938</v>
+        <v>127331094</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>92640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2486,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473748</v>
+        <v>473644</v>
       </c>
       <c r="R17" t="n">
-        <v>6726825</v>
+        <v>6726994</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2549,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331002</v>
+        <v>127330938</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2574,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473724</v>
+        <v>473748</v>
       </c>
       <c r="R18" t="n">
-        <v>6726784</v>
+        <v>6726825</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2659,41 +2654,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331094</v>
+        <v>127331002</v>
       </c>
       <c r="B19" t="n">
-        <v>92639</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473644</v>
+        <v>473724</v>
       </c>
       <c r="R19" t="n">
-        <v>6726994</v>
+        <v>6726784</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2764,46 +2764,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127330814</v>
+        <v>127331196</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>56864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2811,10 +2807,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473929</v>
+        <v>473627</v>
       </c>
       <c r="R20" t="n">
-        <v>6726988</v>
+        <v>6726997</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2855,7 +2851,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2874,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B21" t="n">
-        <v>56864</v>
+        <v>98502</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,31 +2880,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2917,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R21" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2961,6 +2960,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2979,42 +2979,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127331018</v>
+        <v>127330814</v>
       </c>
       <c r="B22" t="n">
-        <v>98501</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473726</v>
+        <v>473929</v>
       </c>
       <c r="R22" t="n">
-        <v>6726792</v>
+        <v>6726988</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3092,7 +3092,7 @@
         <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3749,46 +3749,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331707</v>
+        <v>127331698</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3796,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473813</v>
+        <v>473823</v>
       </c>
       <c r="R29" t="n">
-        <v>6727113</v>
+        <v>6727122</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3834,13 +3830,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,42 +3859,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331698</v>
+        <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3902,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473823</v>
+        <v>473813</v>
       </c>
       <c r="R30" t="n">
-        <v>6727122</v>
+        <v>6727113</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3940,17 +3944,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>127331596</v>
       </c>
       <c r="B31" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>127331652</v>
       </c>
       <c r="B33" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4605,37 +4605,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127331066</v>
+        <v>127330902</v>
       </c>
       <c r="B37" t="n">
-        <v>92639</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4643,10 +4652,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473697</v>
+        <v>473772</v>
       </c>
       <c r="R37" t="n">
-        <v>6726976</v>
+        <v>6726854</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4679,11 +4688,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4711,10 +4715,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330902</v>
+        <v>127330843</v>
       </c>
       <c r="B38" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4741,7 +4745,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4758,10 +4762,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473772</v>
+        <v>473864</v>
       </c>
       <c r="R38" t="n">
-        <v>6726854</v>
+        <v>6726930</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4821,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127330843</v>
+        <v>127331719</v>
       </c>
       <c r="B39" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4851,14 +4855,10 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473864</v>
+        <v>473802</v>
       </c>
       <c r="R39" t="n">
-        <v>6726930</v>
+        <v>6727121</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4931,42 +4931,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331719</v>
+        <v>127331066</v>
       </c>
       <c r="B40" t="n">
-        <v>98467</v>
+        <v>92640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4974,10 +4969,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473802</v>
+        <v>473697</v>
       </c>
       <c r="R40" t="n">
-        <v>6727121</v>
+        <v>6726976</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5010,6 +5005,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -2439,41 +2439,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127331094</v>
+        <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>92640</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2481,10 +2486,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473644</v>
+        <v>473748</v>
       </c>
       <c r="R17" t="n">
-        <v>6726994</v>
+        <v>6726825</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2544,7 +2549,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127330938</v>
+        <v>127331002</v>
       </c>
       <c r="B18" t="n">
         <v>98468</v>
@@ -2574,7 +2579,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473748</v>
+        <v>473724</v>
       </c>
       <c r="R18" t="n">
-        <v>6726825</v>
+        <v>6726784</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2654,46 +2659,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331002</v>
+        <v>127331094</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>92640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473724</v>
+        <v>473644</v>
       </c>
       <c r="R19" t="n">
-        <v>6726784</v>
+        <v>6726994</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B20" t="n">
-        <v>56864</v>
+        <v>98502</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,31 +2775,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2807,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R20" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2851,6 +2855,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2869,10 +2874,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331018</v>
+        <v>127331196</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>56864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,35 +2885,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2916,10 +2917,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473726</v>
+        <v>473627</v>
       </c>
       <c r="R21" t="n">
-        <v>6726792</v>
+        <v>6726997</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2960,7 +2961,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3749,42 +3749,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331698</v>
+        <v>127331707</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3792,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473823</v>
+        <v>473813</v>
       </c>
       <c r="R29" t="n">
-        <v>6727122</v>
+        <v>6727113</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3830,17 +3834,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,46 +3859,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331707</v>
+        <v>127331698</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3906,10 +3902,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473813</v>
+        <v>473823</v>
       </c>
       <c r="R30" t="n">
-        <v>6727113</v>
+        <v>6727122</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3944,13 +3940,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4605,46 +4605,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127330902</v>
+        <v>127331066</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>92640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4652,10 +4643,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473772</v>
+        <v>473697</v>
       </c>
       <c r="R37" t="n">
-        <v>6726854</v>
+        <v>6726976</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4688,6 +4679,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4715,7 +4711,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330843</v>
+        <v>127331719</v>
       </c>
       <c r="B38" t="n">
         <v>98468</v>
@@ -4745,14 +4741,10 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4762,10 +4754,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473864</v>
+        <v>473802</v>
       </c>
       <c r="R38" t="n">
-        <v>6726930</v>
+        <v>6727121</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4825,7 +4817,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127331719</v>
+        <v>127330843</v>
       </c>
       <c r="B39" t="n">
         <v>98468</v>
@@ -4855,10 +4847,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4868,10 +4864,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473802</v>
+        <v>473864</v>
       </c>
       <c r="R39" t="n">
-        <v>6727121</v>
+        <v>6726930</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4931,37 +4927,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331066</v>
+        <v>127330902</v>
       </c>
       <c r="B40" t="n">
-        <v>92640</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473697</v>
+        <v>473772</v>
       </c>
       <c r="R40" t="n">
-        <v>6726976</v>
+        <v>6726854</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5005,11 +5010,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>127304018</v>
       </c>
       <c r="B12" t="n">
-        <v>96593</v>
+        <v>96594</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>127330938</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>127331002</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>127331094</v>
       </c>
       <c r="B19" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331018</v>
+        <v>127331196</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>56864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,35 +2775,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2811,10 +2807,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473726</v>
+        <v>473627</v>
       </c>
       <c r="R20" t="n">
-        <v>6726792</v>
+        <v>6726997</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2855,7 +2851,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2874,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331196</v>
+        <v>127331018</v>
       </c>
       <c r="B21" t="n">
-        <v>56864</v>
+        <v>98503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,31 +2880,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2917,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473627</v>
+        <v>473726</v>
       </c>
       <c r="R21" t="n">
-        <v>6726997</v>
+        <v>6726792</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2961,6 +2960,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>127330814</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>127330753</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>127331745</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>127330976</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3749,46 +3749,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331707</v>
+        <v>127331698</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3796,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473813</v>
+        <v>473823</v>
       </c>
       <c r="R29" t="n">
-        <v>6727113</v>
+        <v>6727122</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3834,13 +3830,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,42 +3859,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331698</v>
+        <v>127331707</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3902,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473823</v>
+        <v>473813</v>
       </c>
       <c r="R30" t="n">
-        <v>6727122</v>
+        <v>6727113</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3940,17 +3944,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>127331596</v>
       </c>
       <c r="B31" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>127331731</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>127331652</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>127331066</v>
       </c>
       <c r="B37" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127331719</v>
+        <v>127330902</v>
       </c>
       <c r="B38" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4741,10 +4741,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4754,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473802</v>
+        <v>473772</v>
       </c>
       <c r="R38" t="n">
-        <v>6727121</v>
+        <v>6726854</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4820,7 +4824,7 @@
         <v>127330843</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4927,10 +4931,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127330902</v>
+        <v>127331719</v>
       </c>
       <c r="B40" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4957,14 +4961,10 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473772</v>
+        <v>473802</v>
       </c>
       <c r="R40" t="n">
-        <v>6726854</v>
+        <v>6727121</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73919856</v>
+        <v>127304018</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalarna, Dlr</t>
+          <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473607.1707076869</v>
+        <v>473699</v>
       </c>
       <c r="R2" t="n">
-        <v>6727474.037186867</v>
+        <v>6726833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,76 +758,74 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96838045</v>
+        <v>127331596</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473653.560135361</v>
+        <v>473535</v>
       </c>
       <c r="R3" t="n">
-        <v>6727041.547541454</v>
+        <v>6727379</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Årsangrepp, ner till ca 2,5 meter. Når ca 3 m upp med yxa</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,47 +863,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Halvliggande vindfälld tall 26 cm med rödbruna barr</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
-        </is>
-      </c>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96838044</v>
+        <v>96838374</v>
       </c>
       <c r="B4" t="n">
-        <v>9009</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,43 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101603</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Furustumpbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plegaderus saucius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Erichson, 1834</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473653.560135361</v>
+        <v>473590</v>
       </c>
       <c r="R4" t="n">
-        <v>6727041.547541454</v>
+        <v>6727070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,24 +950,14 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Samt Nudobius, Rhagium (larver), Acanthacinus (puppor i bark), Trypodendron linetaum (imago, fragment)</t>
+          <t>5 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,16 +972,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Halvliggande vindfälld tall 26 cm med rödbruna barr. Årsangrepp av mindre (och större) märgborre</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,55 +993,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96838046</v>
+        <v>96838375</v>
       </c>
       <c r="B5" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473889.4801305127</v>
+        <v>473896</v>
       </c>
       <c r="R5" t="n">
-        <v>6727021.20412314</v>
+        <v>6727024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,24 +1061,14 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre gnagspår, ner till 2,5 m</t>
+          <t>10 fk i mossa under gammal tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,11 +1083,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Torrtallar 24 &amp; 10 cm</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,19 +1104,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96838375</v>
+        <v>127331066</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1238,19 +1133,22 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473895.390654759</v>
+        <v>473697</v>
       </c>
       <c r="R6" t="n">
-        <v>6727024.101117392</v>
+        <v>6726976</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,27 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>10 fk i mossa under gammal tall</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,80 +1191,74 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
-        </is>
-      </c>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96838376</v>
+        <v>127331094</v>
       </c>
       <c r="B7" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473893.391976978</v>
+        <v>473644</v>
       </c>
       <c r="R7" t="n">
-        <v>6727019.21568875</v>
+        <v>6726994</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,27 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>10 fk i mossa under gammal tall</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,64 +1296,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
-        </is>
-      </c>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96838374</v>
+        <v>96838376</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1496,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473589.9632385883</v>
+        <v>473894</v>
       </c>
       <c r="R8" t="n">
-        <v>6727069.454395373</v>
+        <v>6727019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1529,24 +1383,14 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 fk</t>
+          <t>10 fk i mossa under gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1582,15 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96838043</v>
+        <v>127331652</v>
       </c>
       <c r="B9" t="n">
-        <v>6211</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,42 +1437,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100524</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473589.9632385883</v>
+        <v>473946</v>
       </c>
       <c r="R9" t="n">
-        <v>6727069.454395373</v>
+        <v>6726976</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,27 +1498,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 larv utanpå ticka, i del vänd mot marken</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,46 +1512,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Tallåga 18 cm med citronticka</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
-        </is>
-      </c>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127304107</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1819,53 +1632,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127304344</v>
+        <v>73919860</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NV Stora Snesen, Dlr</t>
+          <t>Dalarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473870</v>
+        <v>473804</v>
       </c>
       <c r="R11" t="n">
-        <v>6726909</v>
+        <v>6727278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1892,12 +1697,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1912,50 +1717,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127304018</v>
+        <v>127331172</v>
       </c>
       <c r="B12" t="n">
-        <v>96594</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1963,13 +1767,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473699</v>
+        <v>473640</v>
       </c>
       <c r="R12" t="n">
-        <v>6726833</v>
+        <v>6727005</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2014,22 +1818,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127304282</v>
+        <v>127331657</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2064,13 +1868,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473559</v>
+        <v>473601</v>
       </c>
       <c r="R13" t="n">
-        <v>6727112</v>
+        <v>6727336</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2115,22 +1919,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127304301</v>
+        <v>73919859</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,37 +1942,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NV Stora Snesen, Dlr</t>
+          <t>Dalarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473659</v>
+        <v>473804</v>
       </c>
       <c r="R14" t="n">
-        <v>6727043</v>
+        <v>6727278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2195,12 +1996,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,29 +2010,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127331366</v>
+        <v>127331133</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473439</v>
+        <v>473662</v>
       </c>
       <c r="R15" t="n">
-        <v>6727269</v>
+        <v>6727012</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2338,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127331172</v>
+        <v>127331366</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,26 +2149,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2376,10 +2181,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473640</v>
+        <v>473439</v>
       </c>
       <c r="R16" t="n">
-        <v>6727005</v>
+        <v>6727269</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2414,13 +2219,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2439,46 +2248,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127330938</v>
+        <v>127331386</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2486,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473748</v>
+        <v>473513</v>
       </c>
       <c r="R17" t="n">
-        <v>6726825</v>
+        <v>6727259</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2524,13 +2329,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2549,46 +2358,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127331002</v>
+        <v>127331403</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2596,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473724</v>
+        <v>473560</v>
       </c>
       <c r="R18" t="n">
-        <v>6726784</v>
+        <v>6727318</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2634,13 +2439,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2659,41 +2468,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127331094</v>
+        <v>127331634</v>
       </c>
       <c r="B19" t="n">
-        <v>92641</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2701,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473644</v>
+        <v>473601</v>
       </c>
       <c r="R19" t="n">
-        <v>6726994</v>
+        <v>6727359</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2739,13 +2549,17 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2764,32 +2578,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127331196</v>
+        <v>127331698</v>
       </c>
       <c r="B20" t="n">
-        <v>56864</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,7 +2611,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2807,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473627</v>
+        <v>473823</v>
       </c>
       <c r="R20" t="n">
-        <v>6726997</v>
+        <v>6727122</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2845,11 +2659,16 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2869,60 +2688,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127331018</v>
+        <v>127360815</v>
       </c>
       <c r="B21" t="n">
-        <v>98503</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NV Stora Snesen, Dlr</t>
+          <t>Djupsjön, Djupsjön, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473726</v>
+        <v>473865</v>
       </c>
       <c r="R21" t="n">
-        <v>6726792</v>
+        <v>6726960</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2954,71 +2766,71 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Foto finns</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127330814</v>
+        <v>127304344</v>
       </c>
       <c r="B22" t="n">
-        <v>98469</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3026,13 +2838,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473929</v>
+        <v>473870</v>
       </c>
       <c r="R22" t="n">
-        <v>6726988</v>
+        <v>6726909</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3070,65 +2882,60 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127330753</v>
+        <v>127331196</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3136,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473944</v>
+        <v>473627</v>
       </c>
       <c r="R23" t="n">
-        <v>6727005</v>
+        <v>6726997</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3180,7 +2987,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3199,46 +3005,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127331745</v>
+        <v>127331217</v>
       </c>
       <c r="B24" t="n">
-        <v>98469</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3246,10 +3048,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473791</v>
+        <v>473606</v>
       </c>
       <c r="R24" t="n">
-        <v>6727140</v>
+        <v>6727012</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3290,7 +3092,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3309,60 +3110,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127330976</v>
+        <v>96838043</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>6284</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100524</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Thunberg, 1784)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473742</v>
+        <v>473590</v>
       </c>
       <c r="R25" t="n">
-        <v>6726796</v>
+        <v>6727070</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3386,12 +3180,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 larv utanpå ticka, i del vänd mot marken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3400,75 +3199,85 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Tallåga 18 cm med citronticka</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127331403</v>
+        <v>96838041</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>4819</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100857</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Robust tickgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dorcatoma robusta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Strand, 1938</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473560</v>
+        <v>473803</v>
       </c>
       <c r="R26" t="n">
-        <v>6727318</v>
+        <v>6727308</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3492,17 +3301,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Kläckhål i ticka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3513,26 +3322,40 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Mosaik av myr, småtjärnar och moränåsar. Här avvikande gran-björksumpskog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe 18 cm med fnösketicka</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127331386</v>
+        <v>96838044</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>9113</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,45 +3363,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>101603</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Furustumpbagge</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Plegaderus saucius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>Erichson, 1834</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473513</v>
+        <v>473653</v>
       </c>
       <c r="R27" t="n">
-        <v>6727259</v>
+        <v>6727041</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3602,17 +3426,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Samt Nudobius, Rhagium (larver), Acanthacinus (puppor i bark), Trypodendron linetaum (imago, fragment)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3623,72 +3447,88 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Halvliggande vindfälld tall 26 cm med rödbruna barr. Årsangrepp av mindre (och större) märgborre</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127331634</v>
+        <v>96838042</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>44177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473601</v>
+        <v>473803</v>
       </c>
       <c r="R28" t="n">
-        <v>6727359</v>
+        <v>6727308</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3712,17 +3552,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Kläckhål vid bas av ticka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3733,72 +3573,78 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Mosaik av myr, småtjärnar och moränåsar. Här avvikande gran-björksumpskog</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe 18 cm med fnösketicka</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127331698</v>
+        <v>73919856</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NV Stora Snesen, Dlr</t>
+          <t>Dalarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473823</v>
+        <v>473607</v>
       </c>
       <c r="R29" t="n">
-        <v>6727122</v>
+        <v>6727474</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3822,24 +3668,19 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Boet är i död björk. 2,2 meter upp.4,5 cm stort bohål. 15 cm djupt bo.</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3847,72 +3688,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127331707</v>
+        <v>73919858</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NV Stora Snesen, Dlr</t>
+          <t>Dalarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473813</v>
+        <v>473789</v>
       </c>
       <c r="R30" t="n">
-        <v>6727113</v>
+        <v>6727297</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3936,12 +3765,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,74 +3779,71 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127331596</v>
+        <v>96838045</v>
       </c>
       <c r="B31" t="n">
-        <v>92635</v>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473535</v>
+        <v>473653</v>
       </c>
       <c r="R31" t="n">
-        <v>6727379</v>
+        <v>6727041</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4041,12 +3867,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Årsangrepp, ner till ca 2,5 meter. Når ca 3 m upp med yxa</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4055,79 +3886,85 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Halvliggande vindfälld tall 26 cm med rödbruna barr</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127331731</v>
+        <v>96838046</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473794</v>
+        <v>473890</v>
       </c>
       <c r="R32" t="n">
-        <v>6727108</v>
+        <v>6727021</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4151,12 +3988,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår, ner till 2,5 m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,60 +4007,78 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Mosaik av myr, småtjärnar och tallmoränåsar</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Torrtallar 24 &amp; 10 cm</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127331652</v>
+        <v>127331018</v>
       </c>
       <c r="B33" t="n">
-        <v>91371</v>
+        <v>99153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4226,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473946</v>
+        <v>473726</v>
       </c>
       <c r="R33" t="n">
-        <v>6726976</v>
+        <v>6726792</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4289,42 +4149,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127331133</v>
+        <v>127330753</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4332,10 +4196,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473662</v>
+        <v>473944</v>
       </c>
       <c r="R34" t="n">
-        <v>6727012</v>
+        <v>6727005</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4370,17 +4234,13 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4399,42 +4259,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127331217</v>
+        <v>127330814</v>
       </c>
       <c r="B35" t="n">
-        <v>56864</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4442,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473606</v>
+        <v>473929</v>
       </c>
       <c r="R35" t="n">
-        <v>6727012</v>
+        <v>6726988</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4486,6 +4350,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4504,37 +4369,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127331657</v>
+        <v>127330843</v>
       </c>
       <c r="B36" t="n">
-        <v>78787</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4542,10 +4416,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473601</v>
+        <v>473864</v>
       </c>
       <c r="R36" t="n">
-        <v>6727336</v>
+        <v>6726930</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4605,37 +4479,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127331066</v>
+        <v>127330902</v>
       </c>
       <c r="B37" t="n">
-        <v>92641</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4643,10 +4526,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473697</v>
+        <v>473772</v>
       </c>
       <c r="R37" t="n">
-        <v>6726976</v>
+        <v>6726854</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4679,11 +4562,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4711,10 +4589,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127330902</v>
+        <v>127330938</v>
       </c>
       <c r="B38" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4741,7 +4619,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4758,10 +4636,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473772</v>
+        <v>473748</v>
       </c>
       <c r="R38" t="n">
-        <v>6726854</v>
+        <v>6726825</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4821,10 +4699,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127330843</v>
+        <v>127330976</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4851,7 +4729,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4868,10 +4746,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473864</v>
+        <v>473742</v>
       </c>
       <c r="R39" t="n">
-        <v>6726930</v>
+        <v>6726796</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4931,10 +4809,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127331719</v>
+        <v>127331002</v>
       </c>
       <c r="B40" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4961,10 +4839,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4974,10 +4856,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473802</v>
+        <v>473724</v>
       </c>
       <c r="R40" t="n">
-        <v>6727121</v>
+        <v>6726784</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5037,53 +4919,60 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127360815</v>
+        <v>127331707</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Dlr</t>
+          <t>NV Stora Snesen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473865</v>
+        <v>473813</v>
       </c>
       <c r="R41" t="n">
-        <v>6726960</v>
+        <v>6727113</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5115,32 +5004,556 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Foto finns</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127331719</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>473802</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6727121</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127331731</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>473794</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6727108</v>
+      </c>
+      <c r="S43" t="n">
+        <v>50</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127331745</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>473791</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6727140</v>
+      </c>
+      <c r="S44" t="n">
+        <v>50</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127304282</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>473559</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6727112</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127304301</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>NV Stora Snesen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>473659</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6727043</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33685-2025 artfynd.xlsx
+++ b/artfynd/A 33685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838375</t>
         </is>
       </c>
     </row>
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331066</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331094</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838376</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331652</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304107</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919860</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331172</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331657</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919859</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331133</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331366</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2250,6 +2325,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331386</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2360,6 +2440,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331403</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2470,6 +2555,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331698</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2577,6 +2667,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360815</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2682,6 +2777,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304344</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2787,6 +2887,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331196</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,6 +2997,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331217</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3013,6 +3123,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838043</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3134,6 +3249,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838041</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3264,6 +3384,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838044</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3385,6 +3510,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838042</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3482,6 +3612,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919858</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3603,6 +3738,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838045</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3724,6 +3864,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838046</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3834,6 +3979,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331018</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3944,6 +4094,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127330753</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4054,6 +4209,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127330814</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4164,6 +4324,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127330843</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4274,6 +4439,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127330902</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4384,6 +4554,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127330938</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4494,6 +4669,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127330976</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4604,6 +4784,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331002</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4714,6 +4899,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331707</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4820,6 +5010,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331719</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4930,6 +5125,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331731</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5040,6 +5240,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331745</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5141,6 +5346,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304282</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5242,6 +5452,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304301</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5347,6 +5562,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331596</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5457,6 +5677,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127331634</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5554,8 +5779,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919856</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>